--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1684" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1684" uniqueCount="373">
   <si>
     <t>50001559 - FERROVIAL</t>
   </si>
@@ -830,6 +830,9 @@
   </si>
   <si>
     <t>OT 4347 Armado</t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1215506984982888</t>
@@ -6223,7 +6226,7 @@
         <v>46225.806332569446</v>
       </c>
       <c r="D78" s="5">
-        <v>46277.48308394676</v>
+        <v>46281.13541505787</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>250</v>
@@ -6267,8 +6270,8 @@
       <c r="R78" s="5">
         <v>46288</v>
       </c>
-      <c r="S78" s="10" t="s">
-        <v>32</v>
+      <c r="S78" s="12" t="s">
+        <v>251</v>
       </c>
       <c r="T78" s="6">
         <v>1</v>
@@ -6279,7 +6282,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B79" s="8">
         <v>46181.60925648148</v>
@@ -6321,10 +6324,10 @@
         <v>250</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -6334,7 +6337,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B80" s="5">
         <v>46181.609262199076</v>
@@ -6376,10 +6379,10 @@
         <v>250</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6389,7 +6392,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B81" s="8">
         <v>46181.60926783565</v>
@@ -6401,7 +6404,7 @@
         <v>46277.48311030093</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6454,7 +6457,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B82" s="5">
         <v>46181.60927226851</v>
@@ -6493,13 +6496,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6509,7 +6512,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B83" s="8">
         <v>46181.60927799769</v>
@@ -6548,13 +6551,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6564,7 +6567,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B84" s="5">
         <v>46181.60928361111</v>
@@ -6600,7 +6603,7 @@
         <v>26</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -6617,7 +6620,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B85" s="8">
         <v>46181.609286990744</v>
@@ -6629,7 +6632,7 @@
         <v>46213.56773226852</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
@@ -6662,7 +6665,7 @@
         <v>26</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q85" s="8">
         <v>46182</v>
@@ -6682,7 +6685,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B86" s="5">
         <v>46181.609292974535</v>
@@ -6694,7 +6697,7 @@
         <v>46213.56774653935</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6727,7 +6730,7 @@
         <v>26</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q86" s="5">
         <v>46290</v>
@@ -6747,7 +6750,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B87" s="8">
         <v>46181.60929881944</v>
@@ -6759,7 +6762,7 @@
         <v>46228.196411377314</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
@@ -6792,7 +6795,7 @@
         <v>26</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q87" s="8">
         <v>46226</v>
@@ -6812,7 +6815,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B88" s="5">
         <v>46181.60930480324</v>
@@ -6822,7 +6825,7 @@
         <v>46252.6315703125</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6855,7 +6858,7 @@
         <v>158</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q88" s="5">
         <v>46293</v>
@@ -6875,7 +6878,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B89" s="8">
         <v>46181.60935271991</v>
@@ -6940,7 +6943,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B90" s="5">
         <v>46181.60936674768</v>
@@ -6950,7 +6953,7 @@
         <v>46252.63140201389</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>25</v>
@@ -6974,7 +6977,7 @@
         <v>26</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>26</v>
@@ -6987,7 +6990,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B91" s="8">
         <v>46181.609371666666</v>
@@ -6999,7 +7002,7 @@
         <v>46252.631576087966</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
@@ -7026,13 +7029,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q91" s="8">
         <v>46290</v>
@@ -7052,7 +7055,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B92" s="5">
         <v>46181.609378587964</v>
@@ -7089,13 +7092,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7105,7 +7108,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B93" s="8">
         <v>46181.61514019676</v>
@@ -7142,13 +7145,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O93" s="9" t="s">
         <v>181</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -7158,7 +7161,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B94" s="5">
         <v>46181.609386111115</v>
@@ -7170,7 +7173,7 @@
         <v>46223.56717594907</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7197,13 +7200,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>181</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q94" s="5">
         <v>46311</v>
@@ -7223,7 +7226,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B95" s="8">
         <v>46181.60939194444</v>
@@ -7262,13 +7265,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7278,7 +7281,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B96" s="5">
         <v>46181.61518315972</v>
@@ -7317,10 +7320,10 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>26</v>
@@ -7333,7 +7336,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B97" s="8">
         <v>46181.60939866898</v>
@@ -7345,7 +7348,7 @@
         <v>46260.58895535879</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
@@ -7372,13 +7375,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O97" s="9" t="s">
         <v>181</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q97" s="8">
         <v>46315</v>
@@ -7398,7 +7401,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B98" s="5">
         <v>46181.60940505787</v>
@@ -7437,13 +7440,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7453,7 +7456,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B99" s="8">
         <v>46181.61523613426</v>
@@ -7492,10 +7495,10 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P99" s="9" t="s">
         <v>26</v>
@@ -7508,7 +7511,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B100" s="5">
         <v>46181.60941365741</v>
@@ -7520,7 +7523,7 @@
         <v>46252.631415497686</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7547,13 +7550,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O100" s="6" t="s">
         <v>181</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q100" s="5">
         <v>46317</v>
@@ -7573,7 +7576,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B101" s="8">
         <v>46181.60941929398</v>
@@ -7610,13 +7613,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7626,7 +7629,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B102" s="5">
         <v>46181.61528053241</v>
@@ -7663,10 +7666,10 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>26</v>
@@ -7679,7 +7682,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B103" s="8">
         <v>46181.60942706019</v>
@@ -7689,7 +7692,7 @@
         <v>46260.588979409724</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
@@ -7716,13 +7719,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O103" s="9" t="s">
         <v>181</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q103" s="8">
         <v>46321</v>
@@ -7742,7 +7745,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B104" s="5">
         <v>46181.60943415509</v>
@@ -7779,13 +7782,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O104" s="6" t="s">
         <v>181</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7795,7 +7798,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B105" s="8">
         <v>46181.61532783565</v>
@@ -7832,7 +7835,7 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O105" s="9" t="s">
         <v>181</v>
@@ -7848,7 +7851,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B106" s="5">
         <v>46181.60944410879</v>
@@ -7858,7 +7861,7 @@
         <v>46260.58900550926</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7885,13 +7888,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>181</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q106" s="5">
         <v>46323</v>
@@ -7911,7 +7914,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B107" s="8">
         <v>46181.60944996528</v>
@@ -7948,13 +7951,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O107" s="9" t="s">
         <v>181</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -7964,7 +7967,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B108" s="5">
         <v>46181.61537143518</v>
@@ -8001,7 +8004,7 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O108" s="6" t="s">
         <v>213</v>
@@ -8017,7 +8020,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B109" s="8">
         <v>46181.60945642361</v>
@@ -8027,7 +8030,7 @@
         <v>46252.63173365741</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>25</v>
@@ -8051,7 +8054,7 @@
         <v>26</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P109" s="9" t="s">
         <v>26</v>
@@ -8064,7 +8067,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B110" s="5">
         <v>46181.60946096065</v>
@@ -8076,16 +8079,16 @@
         <v>46252.63174694445</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="I110" s="5">
         <v>46324</v>
@@ -8103,13 +8106,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q110" s="5">
         <v>46324</v>
@@ -8129,7 +8132,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B111" s="8">
         <v>46181.60946868056</v>
@@ -8145,10 +8148,10 @@
         <v>26</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H111" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="I111" s="8">
         <v>46324</v>
@@ -8166,13 +8169,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O111" s="9" t="s">
         <v>181</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q111" s="9"/>
       <c r="R111" s="9"/>
@@ -8182,7 +8185,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B112" s="5">
         <v>46181.609475034726</v>
@@ -8198,10 +8201,10 @@
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="I112" s="5">
         <v>46324</v>
@@ -8219,7 +8222,7 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O112" s="6" t="s">
         <v>181</v>
@@ -8235,7 +8238,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B113" s="8">
         <v>46181.60947921296</v>
@@ -8251,10 +8254,10 @@
         <v>26</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H113" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="I113" s="8">
         <v>46324</v>
@@ -8272,7 +8275,7 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O113" s="9" t="s">
         <v>61</v>
@@ -8288,7 +8291,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B114" s="5">
         <v>46181.61605960648</v>
@@ -8304,10 +8307,10 @@
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="I114" s="5">
         <v>46324</v>
@@ -8325,7 +8328,7 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O114" s="6" t="s">
         <v>61</v>
@@ -8341,7 +8344,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B115" s="8">
         <v>46181.61617203704</v>
@@ -8357,10 +8360,10 @@
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H115" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="I115" s="8">
         <v>46324</v>
@@ -8378,7 +8381,7 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O115" s="9" t="s">
         <v>26</v>
@@ -8394,7 +8397,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B116" s="5">
         <v>46181.61620771991</v>
@@ -8410,10 +8413,10 @@
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="I116" s="5">
         <v>46324</v>
@@ -8431,7 +8434,7 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O116" s="6" t="s">
         <v>26</v>
@@ -8447,7 +8450,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B117" s="8">
         <v>46181.616245833335</v>
@@ -8457,16 +8460,16 @@
         <v>46231.86380424768</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H117" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="I117" s="8">
         <v>46324</v>
@@ -8484,7 +8487,7 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O117" s="9" t="s">
         <v>26</v>
@@ -8500,7 +8503,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B118" s="5">
         <v>46181.60948424769</v>
@@ -8510,7 +8513,7 @@
         <v>46260.589110138884</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8537,13 +8540,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O118" s="6" t="s">
         <v>181</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q118" s="5">
         <v>46325</v>
@@ -8563,7 +8566,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B119" s="8">
         <v>46181.60948969907</v>
@@ -8600,13 +8603,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O119" s="9" t="s">
         <v>181</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q119" s="9"/>
       <c r="R119" s="9"/>
@@ -8616,7 +8619,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B120" s="5">
         <v>46181.60949538194</v>
@@ -8653,7 +8656,7 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>181</v>
@@ -8669,7 +8672,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B121" s="8">
         <v>46181.609560185185</v>
@@ -8706,7 +8709,7 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O121" s="9" t="s">
         <v>61</v>
@@ -8722,7 +8725,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B122" s="5">
         <v>46181.61659114584</v>
@@ -8759,7 +8762,7 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O122" s="6" t="s">
         <v>61</v>
@@ -8775,7 +8778,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B123" s="8">
         <v>46181.61662431713</v>
@@ -8812,7 +8815,7 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O123" s="9" t="s">
         <v>186</v>
@@ -8828,7 +8831,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B124" s="5">
         <v>46181.61666238426</v>
@@ -8865,7 +8868,7 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O124" s="6" t="s">
         <v>189</v>
@@ -8881,7 +8884,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B125" s="8">
         <v>46181.61670006944</v>
@@ -8918,10 +8921,10 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P125" s="9" t="s">
         <v>191</v>
@@ -8934,7 +8937,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B126" s="5">
         <v>46181.60956560185</v>
@@ -8944,7 +8947,7 @@
         <v>46260.58912837963</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -8971,13 +8974,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O126" s="6" t="s">
         <v>181</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q126" s="5">
         <v>46328</v>
@@ -8997,7 +9000,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B127" s="8">
         <v>46181.60957188657</v>
@@ -9034,13 +9037,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O127" s="9" t="s">
         <v>181</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q127" s="9"/>
       <c r="R127" s="9"/>
@@ -9050,7 +9053,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B128" s="5">
         <v>46181.609583576384</v>
@@ -9087,7 +9090,7 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O128" s="6" t="s">
         <v>181</v>
@@ -9103,7 +9106,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B129" s="8">
         <v>46181.60958841435</v>
@@ -9140,7 +9143,7 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O129" s="9" t="s">
         <v>61</v>
@@ -9156,7 +9159,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B130" s="5">
         <v>46181.616839849536</v>
@@ -9193,7 +9196,7 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O130" s="6" t="s">
         <v>61</v>
@@ -9209,7 +9212,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B131" s="8">
         <v>46181.61689748843</v>
@@ -9246,7 +9249,7 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O131" s="9" t="s">
         <v>186</v>
@@ -9262,7 +9265,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B132" s="5">
         <v>46181.616942569446</v>
@@ -9299,7 +9302,7 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O132" s="6" t="s">
         <v>189</v>
@@ -9315,7 +9318,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B133" s="8">
         <v>46181.6169815162</v>
@@ -9352,7 +9355,7 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O133" s="9" t="s">
         <v>191</v>
@@ -9368,7 +9371,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B134" s="5">
         <v>46181.609592673616</v>
@@ -9378,7 +9381,7 @@
         <v>46260.58917085648</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9405,13 +9408,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O134" s="6" t="s">
         <v>181</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q134" s="5">
         <v>46329</v>
@@ -9431,7 +9434,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B135" s="8">
         <v>46181.60960517361</v>
@@ -9468,13 +9471,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O135" s="9" t="s">
         <v>181</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q135" s="9"/>
       <c r="R135" s="9"/>
@@ -9484,7 +9487,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B136" s="5">
         <v>46181.609610011576</v>
@@ -9521,7 +9524,7 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O136" s="6" t="s">
         <v>181</v>
@@ -9537,7 +9540,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B137" s="8">
         <v>46181.609613796296</v>
@@ -9574,7 +9577,7 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O137" s="9" t="s">
         <v>61</v>
@@ -9590,7 +9593,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B138" s="5">
         <v>46181.61712142361</v>
@@ -9627,7 +9630,7 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O138" s="6" t="s">
         <v>61</v>
@@ -9643,7 +9646,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B139" s="8">
         <v>46181.61716094907</v>
@@ -9680,7 +9683,7 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O139" s="9" t="s">
         <v>186</v>
@@ -9696,7 +9699,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B140" s="5">
         <v>46181.61719633102</v>
@@ -9733,7 +9736,7 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O140" s="6" t="s">
         <v>189</v>
@@ -9749,7 +9752,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B141" s="8">
         <v>46181.617235451384</v>
@@ -9786,7 +9789,7 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O141" s="9" t="s">
         <v>191</v>
@@ -9802,7 +9805,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B142" s="5">
         <v>46181.60961741898</v>
@@ -9812,7 +9815,7 @@
         <v>46182.63449439815</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>25</v>
@@ -9836,7 +9839,7 @@
         <v>26</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P142" s="6" t="s">
         <v>26</v>
@@ -9849,7 +9852,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B143" s="8">
         <v>46181.60962174769</v>
@@ -9859,16 +9862,16 @@
         <v>46182.64244836806</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="I143" s="8">
         <v>46330</v>
@@ -9886,13 +9889,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O143" s="9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q143" s="8">
         <v>46330</v>
@@ -9912,7 +9915,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B144" s="5">
         <v>46181.60962780092</v>
@@ -9922,7 +9925,7 @@
         <v>46191.67892958333</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -9949,13 +9952,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q144" s="5">
         <v>46330</v>

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -6401,7 +6401,7 @@
         <v>46226.72501033565</v>
       </c>
       <c r="D81" s="8">
-        <v>46277.48311030093</v>
+        <v>46282.13434399306</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>257</v>
@@ -6445,8 +6445,8 @@
       <c r="R81" s="8">
         <v>46289</v>
       </c>
-      <c r="S81" s="10" t="s">
-        <v>32</v>
+      <c r="S81" s="12" t="s">
+        <v>251</v>
       </c>
       <c r="T81" s="9">
         <v>1</v>

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -544,6 +544,9 @@
     <t>Fabricación estructura proveedor externo ot 4347,Generacion OC Fabricación Externa ot 4347</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1215506819661464</t>
   </si>
   <si>
@@ -830,9 +833,6 @@
   </si>
   <si>
     <t>OT 4347 Armado</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1215506984982888</t>
@@ -4081,7 +4081,7 @@
         <v>46204.67472811343</v>
       </c>
       <c r="D41" s="8">
-        <v>46212.82441381944</v>
+        <v>46283.164668020836</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>151</v>
@@ -4125,8 +4125,8 @@
       <c r="R41" s="8">
         <v>46290</v>
       </c>
-      <c r="S41" s="10" t="s">
-        <v>32</v>
+      <c r="S41" s="12" t="s">
+        <v>155</v>
       </c>
       <c r="T41" s="9">
         <v>1</v>
@@ -4137,7 +4137,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B42" s="5">
         <v>46181.60905075232</v>
@@ -4182,7 +4182,7 @@
         <v>105</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4192,7 +4192,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B43" s="8">
         <v>46181.60905546296</v>
@@ -4204,7 +4204,7 @@
         <v>46204.67391837963</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
@@ -4237,7 +4237,7 @@
         <v>106</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
@@ -4247,7 +4247,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B44" s="5">
         <v>46181.60906018519</v>
@@ -4257,16 +4257,16 @@
         <v>46204.67384744213</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I44" s="5">
         <v>46290</v>
@@ -4287,7 +4287,7 @@
         <v>151</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>26</v>
@@ -4300,7 +4300,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B45" s="8">
         <v>46181.609063310185</v>
@@ -4312,7 +4312,7 @@
         <v>46263.18757858797</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
@@ -4342,7 +4342,7 @@
         <v>119</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P45" s="9" t="s">
         <v>26</v>
@@ -4365,7 +4365,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B46" s="5">
         <v>46181.60906703703</v>
@@ -4404,13 +4404,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>102</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4420,7 +4420,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B47" s="8">
         <v>46181.60907681713</v>
@@ -4432,7 +4432,7 @@
         <v>46205.612879328706</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
@@ -4459,13 +4459,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O47" s="9" t="s">
         <v>103</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q47" s="9"/>
       <c r="R47" s="9"/>
@@ -4475,7 +4475,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B48" s="5">
         <v>46181.6090815625</v>
@@ -4487,7 +4487,7 @@
         <v>46210.525643402776</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>25</v>
@@ -4511,7 +4511,7 @@
         <v>26</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>26</v>
@@ -4528,7 +4528,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B49" s="8">
         <v>46181.60908480324</v>
@@ -4540,16 +4540,16 @@
         <v>46197.7158150926</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I49" s="8">
         <v>46174</v>
@@ -4567,13 +4567,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q49" s="8">
         <v>46174</v>
@@ -4593,7 +4593,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B50" s="5">
         <v>46181.60908915509</v>
@@ -4605,16 +4605,16 @@
         <v>46190.70821390046</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I50" s="5">
         <v>46174</v>
@@ -4632,13 +4632,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4648,7 +4648,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B51" s="8">
         <v>46181.60909384259</v>
@@ -4660,16 +4660,16 @@
         <v>46190.7082228125</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I51" s="8">
         <v>46174</v>
@@ -4687,13 +4687,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O51" s="9" t="s">
         <v>78</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -4703,7 +4703,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B52" s="5">
         <v>46181.61221741898</v>
@@ -4715,16 +4715,16 @@
         <v>46190.708227337964</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I52" s="5">
         <v>46174</v>
@@ -4742,13 +4742,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4758,7 +4758,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B53" s="8">
         <v>46181.612357199076</v>
@@ -4770,16 +4770,16 @@
         <v>46190.708233321755</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I53" s="8">
         <v>46174</v>
@@ -4797,13 +4797,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O53" s="9" t="s">
         <v>78</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -4813,7 +4813,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B54" s="5">
         <v>46181.609098182875</v>
@@ -4825,16 +4825,16 @@
         <v>46247.20374798611</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I54" s="5">
         <v>46227</v>
@@ -4852,13 +4852,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q54" s="5">
         <v>46227</v>
@@ -4878,7 +4878,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B55" s="8">
         <v>46181.60910252314</v>
@@ -4890,16 +4890,16 @@
         <v>46191.54270819444</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I55" s="8">
         <v>46227</v>
@@ -4917,13 +4917,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -4933,7 +4933,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B56" s="5">
         <v>46181.609107951386</v>
@@ -4945,16 +4945,16 @@
         <v>46191.54271703704</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I56" s="5">
         <v>46227</v>
@@ -4972,13 +4972,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4988,7 +4988,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B57" s="8">
         <v>46181.61393570602</v>
@@ -5000,16 +5000,16 @@
         <v>46190.70842170139</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I57" s="8">
         <v>46227</v>
@@ -5027,13 +5027,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5043,7 +5043,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B58" s="5">
         <v>46181.61396929398</v>
@@ -5055,16 +5055,16 @@
         <v>46190.708426550926</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I58" s="5">
         <v>46227</v>
@@ -5082,13 +5082,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5098,7 +5098,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B59" s="8">
         <v>46181.60911329861</v>
@@ -5116,10 +5116,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I59" s="8">
         <v>46247</v>
@@ -5137,13 +5137,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q59" s="8">
         <v>46247</v>
@@ -5163,7 +5163,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B60" s="5">
         <v>46181.60912350695</v>
@@ -5175,16 +5175,16 @@
         <v>46191.54536050926</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I60" s="6"/>
       <c r="J60" s="5">
@@ -5203,7 +5203,7 @@
         <v>96</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>96</v>
@@ -5216,7 +5216,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B61" s="8">
         <v>46181.60912782408</v>
@@ -5228,16 +5228,16 @@
         <v>46191.54537386574</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I61" s="9"/>
       <c r="J61" s="8">
@@ -5256,7 +5256,7 @@
         <v>96</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>96</v>
@@ -5269,7 +5269,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B62" s="5">
         <v>46181.614119606485</v>
@@ -5281,16 +5281,16 @@
         <v>46190.721725358795</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I62" s="6"/>
       <c r="J62" s="5">
@@ -5309,7 +5309,7 @@
         <v>96</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5322,7 +5322,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B63" s="8">
         <v>46181.61419627315</v>
@@ -5334,16 +5334,16 @@
         <v>46190.7217299537</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I63" s="9"/>
       <c r="J63" s="8">
@@ -5362,7 +5362,7 @@
         <v>96</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5375,7 +5375,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B64" s="5">
         <v>46181.60913207176</v>
@@ -5387,16 +5387,16 @@
         <v>46258.54296335648</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I64" s="5">
         <v>46322</v>
@@ -5414,10 +5414,10 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>26</v>
@@ -5440,7 +5440,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B65" s="8">
         <v>46181.609135833336</v>
@@ -5450,16 +5450,16 @@
         <v>46182.63311847222</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I65" s="8">
         <v>46322</v>
@@ -5477,13 +5477,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="9"/>
@@ -5493,7 +5493,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B66" s="5">
         <v>46181.614311909725</v>
@@ -5503,16 +5503,16 @@
         <v>46182.63311923611</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I66" s="5">
         <v>46322</v>
@@ -5530,13 +5530,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5546,7 +5546,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B67" s="8">
         <v>46181.60918671296</v>
@@ -5558,7 +5558,7 @@
         <v>46216.64129429398</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>25</v>
@@ -5582,7 +5582,7 @@
         <v>26</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P67" s="9" t="s">
         <v>26</v>
@@ -5599,7 +5599,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B68" s="5">
         <v>46181.609196087964</v>
@@ -5611,16 +5611,16 @@
         <v>46254.18670849537</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I68" s="5">
         <v>46252</v>
@@ -5638,13 +5638,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>140</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q68" s="5">
         <v>46252</v>
@@ -5664,7 +5664,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B69" s="8">
         <v>46181.609201921296</v>
@@ -5676,16 +5676,16 @@
         <v>46256.19373965278</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I69" s="8">
         <v>46254</v>
@@ -5703,13 +5703,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q69" s="8">
         <v>46254</v>
@@ -5729,7 +5729,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B70" s="5">
         <v>46181.60920746528</v>
@@ -5741,16 +5741,16 @@
         <v>46254.18670847222</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I70" s="5">
         <v>46252</v>
@@ -5768,13 +5768,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>148</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q70" s="5">
         <v>46252</v>
@@ -5794,7 +5794,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B71" s="8">
         <v>46181.609212870375</v>
@@ -5806,16 +5806,16 @@
         <v>46256.19373966435</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I71" s="8">
         <v>46254</v>
@@ -5833,13 +5833,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q71" s="8">
         <v>46254</v>
@@ -5859,7 +5859,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B72" s="5">
         <v>46181.60921715278</v>
@@ -5871,16 +5871,16 @@
         <v>46254.18670752315</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I72" s="5">
         <v>46252</v>
@@ -5898,13 +5898,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q72" s="5">
         <v>46252</v>
@@ -5924,7 +5924,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B73" s="8">
         <v>46181.60922180556</v>
@@ -5936,16 +5936,16 @@
         <v>46256.19373991898</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I73" s="8">
         <v>46254</v>
@@ -5963,13 +5963,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q73" s="8">
         <v>46254</v>
@@ -5989,7 +5989,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B74" s="5">
         <v>46181.60922590278</v>
@@ -6001,7 +6001,7 @@
         <v>46226.725049155095</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>25</v>
@@ -6025,7 +6025,7 @@
         <v>26</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>26</v>
@@ -6042,7 +6042,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B75" s="8">
         <v>46181.60922940972</v>
@@ -6054,16 +6054,16 @@
         <v>46277.483034930556</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I75" s="8">
         <v>46258</v>
@@ -6081,13 +6081,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q75" s="8">
         <v>46258</v>
@@ -6107,7 +6107,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B76" s="5">
         <v>46181.60923553241</v>
@@ -6119,16 +6119,16 @@
         <v>46225.8062046875</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I76" s="5">
         <v>46258</v>
@@ -6146,13 +6146,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6162,7 +6162,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B77" s="8">
         <v>46181.609241805556</v>
@@ -6174,16 +6174,16 @@
         <v>46225.806214282406</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I77" s="8">
         <v>46258</v>
@@ -6201,13 +6201,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q77" s="9"/>
       <c r="R77" s="9"/>
@@ -6217,7 +6217,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B78" s="5">
         <v>46181.609247002314</v>
@@ -6229,16 +6229,16 @@
         <v>46281.13541505787</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I78" s="5">
         <v>46267</v>
@@ -6256,13 +6256,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q78" s="5">
         <v>46267</v>
@@ -6271,7 +6271,7 @@
         <v>46288</v>
       </c>
       <c r="S78" s="12" t="s">
-        <v>251</v>
+        <v>155</v>
       </c>
       <c r="T78" s="6">
         <v>1</v>
@@ -6294,16 +6294,16 @@
         <v>46225.806309120366</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I79" s="8">
         <v>46267</v>
@@ -6321,7 +6321,7 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O79" s="9" t="s">
         <v>253</v>
@@ -6349,16 +6349,16 @@
         <v>46225.806319490744</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I80" s="5">
         <v>46267</v>
@@ -6376,7 +6376,7 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>253</v>
@@ -6410,10 +6410,10 @@
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I81" s="8">
         <v>46289</v>
@@ -6431,13 +6431,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q81" s="8">
         <v>46289</v>
@@ -6446,7 +6446,7 @@
         <v>46289</v>
       </c>
       <c r="S81" s="12" t="s">
-        <v>251</v>
+        <v>155</v>
       </c>
       <c r="T81" s="9">
         <v>1</v>
@@ -6469,16 +6469,16 @@
         <v>46226.72551587963</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I82" s="5">
         <v>46289</v>
@@ -6524,16 +6524,16 @@
         <v>46226.72552325232</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I83" s="8">
         <v>46289</v>
@@ -6579,7 +6579,7 @@
         <v>46252.63149832176</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>25</v>
@@ -6638,10 +6638,10 @@
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I85" s="8">
         <v>46182</v>
@@ -6659,7 +6659,7 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O85" s="9" t="s">
         <v>26</v>
@@ -6703,10 +6703,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I86" s="5">
         <v>46290</v>
@@ -6724,7 +6724,7 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>26</v>
@@ -6768,10 +6768,10 @@
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I87" s="8">
         <v>46226</v>
@@ -6789,7 +6789,7 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O87" s="9" t="s">
         <v>26</v>
@@ -6831,10 +6831,10 @@
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I88" s="5">
         <v>46293</v>
@@ -6852,10 +6852,10 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>273</v>
@@ -6896,10 +6896,10 @@
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I89" s="8">
         <v>46226</v>
@@ -6917,7 +6917,7 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O89" s="9" t="s">
         <v>129</v>
@@ -7065,7 +7065,7 @@
         <v>46252.631576388885</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7118,7 +7118,7 @@
         <v>46226.725527256945</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
@@ -7148,7 +7148,7 @@
         <v>279</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P93" s="9" t="s">
         <v>284</v>
@@ -7203,7 +7203,7 @@
         <v>276</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>276</v>
@@ -7238,7 +7238,7 @@
         <v>46223.566525462964</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
@@ -7293,7 +7293,7 @@
         <v>46223.56652129629</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7378,7 +7378,7 @@
         <v>276</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P97" s="9" t="s">
         <v>276</v>
@@ -7413,7 +7413,7 @@
         <v>46223.56665253472</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7468,7 +7468,7 @@
         <v>46223.56667947916</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
@@ -7553,7 +7553,7 @@
         <v>276</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P100" s="6" t="s">
         <v>276</v>
@@ -7586,7 +7586,7 @@
         <v>46223.566807800926</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
@@ -7639,7 +7639,7 @@
         <v>46223.56680710649</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7722,7 +7722,7 @@
         <v>276</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P103" s="9" t="s">
         <v>276</v>
@@ -7755,7 +7755,7 @@
         <v>46223.566960972224</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7785,7 +7785,7 @@
         <v>307</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P104" s="6" t="s">
         <v>309</v>
@@ -7808,7 +7808,7 @@
         <v>46223.56696034722</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
@@ -7838,10 +7838,10 @@
         <v>307</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -7891,7 +7891,7 @@
         <v>276</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>313</v>
@@ -7924,7 +7924,7 @@
         <v>46223.56705920139</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
@@ -7954,7 +7954,7 @@
         <v>312</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P107" s="9" t="s">
         <v>315</v>
@@ -7977,7 +7977,7 @@
         <v>46223.56705859954</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -8007,7 +8007,7 @@
         <v>312</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>26</v>
@@ -8142,7 +8142,7 @@
         <v>46182.641845254635</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
@@ -8172,7 +8172,7 @@
         <v>321</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P111" s="9" t="s">
         <v>326</v>
@@ -8195,7 +8195,7 @@
         <v>46226.725528553245</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8225,10 +8225,10 @@
         <v>321</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8354,7 +8354,7 @@
         <v>46231.862803634256</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
@@ -8387,7 +8387,7 @@
         <v>26</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q115" s="9"/>
       <c r="R115" s="9"/>
@@ -8407,7 +8407,7 @@
         <v>46216.715609837964</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8440,7 +8440,7 @@
         <v>26</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8493,7 +8493,7 @@
         <v>26</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8543,7 +8543,7 @@
         <v>318</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>318</v>
@@ -8576,7 +8576,7 @@
         <v>46223.56727827546</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
@@ -8606,7 +8606,7 @@
         <v>335</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P119" s="9" t="s">
         <v>337</v>
@@ -8629,7 +8629,7 @@
         <v>46223.567277685186</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8659,10 +8659,10 @@
         <v>335</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8788,7 +8788,7 @@
         <v>46223.56727590278</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
@@ -8818,10 +8818,10 @@
         <v>335</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q123" s="9"/>
       <c r="R123" s="9"/>
@@ -8841,7 +8841,7 @@
         <v>46223.56727532407</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8871,10 +8871,10 @@
         <v>335</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8894,7 +8894,7 @@
         <v>46223.56727472223</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
@@ -8927,7 +8927,7 @@
         <v>333</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q125" s="9"/>
       <c r="R125" s="9"/>
@@ -8953,10 +8953,10 @@
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I126" s="5">
         <v>46328</v>
@@ -8977,7 +8977,7 @@
         <v>318</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>318</v>
@@ -9010,16 +9010,16 @@
         <v>46182.82945300926</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H127" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I127" s="8">
         <v>46328</v>
@@ -9040,7 +9040,7 @@
         <v>345</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P127" s="9" t="s">
         <v>347</v>
@@ -9063,16 +9063,16 @@
         <v>46182.829453784725</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I128" s="5">
         <v>46328</v>
@@ -9093,10 +9093,10 @@
         <v>345</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9122,10 +9122,10 @@
         <v>26</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H129" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I129" s="8">
         <v>46328</v>
@@ -9175,10 +9175,10 @@
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I130" s="5">
         <v>46328</v>
@@ -9222,16 +9222,16 @@
         <v>46182.8294564699</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H131" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I131" s="8">
         <v>46328</v>
@@ -9252,10 +9252,10 @@
         <v>345</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q131" s="9"/>
       <c r="R131" s="9"/>
@@ -9275,16 +9275,16 @@
         <v>46182.82945721065</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I132" s="5">
         <v>46328</v>
@@ -9305,10 +9305,10 @@
         <v>345</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9328,16 +9328,16 @@
         <v>46182.82945796296</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H133" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I133" s="8">
         <v>46328</v>
@@ -9358,10 +9358,10 @@
         <v>345</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9387,10 +9387,10 @@
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I134" s="5">
         <v>46329</v>
@@ -9411,7 +9411,7 @@
         <v>318</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P134" s="6" t="s">
         <v>356</v>
@@ -9444,16 +9444,16 @@
         <v>46182.8294527199</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H135" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I135" s="8">
         <v>46329</v>
@@ -9474,7 +9474,7 @@
         <v>355</v>
       </c>
       <c r="O135" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P135" s="9" t="s">
         <v>355</v>
@@ -9497,16 +9497,16 @@
         <v>46182.829451909725</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I136" s="5">
         <v>46329</v>
@@ -9527,7 +9527,7 @@
         <v>355</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P136" s="6" t="s">
         <v>26</v>
@@ -9556,10 +9556,10 @@
         <v>26</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H137" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I137" s="8">
         <v>46329</v>
@@ -9609,10 +9609,10 @@
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I138" s="5">
         <v>46329</v>
@@ -9656,16 +9656,16 @@
         <v>46182.82945207176</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H139" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I139" s="8">
         <v>46329</v>
@@ -9686,7 +9686,7 @@
         <v>355</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P139" s="9" t="s">
         <v>26</v>
@@ -9709,16 +9709,16 @@
         <v>46182.829452025464</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I140" s="5">
         <v>46329</v>
@@ -9739,7 +9739,7 @@
         <v>355</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P140" s="6" t="s">
         <v>26</v>
@@ -9762,16 +9762,16 @@
         <v>46182.829452418984</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H141" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I141" s="8">
         <v>46329</v>
@@ -9792,7 +9792,7 @@
         <v>355</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P141" s="9" t="s">
         <v>26</v>
